--- a/employment_xlsx/PECH_HACKATHON_RULES_AND_GUIDELINES.xlsx
+++ b/employment_xlsx/PECH_HACKATHON_RULES_AND_GUIDELINES.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +59,34 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000099CC"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00F5A623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00888888"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00E8F4F8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="7"/>
     </font>
   </fonts>
   <fills count="8">
@@ -131,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -162,6 +190,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -236,6 +279,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1905000" cy="628650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -525,8 +598,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -545,63 +619,31 @@
     <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="6" customHeight="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr"/>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr"/>
-      <c r="H1" s="1" t="inlineStr"/>
-      <c r="I1" s="1" t="inlineStr"/>
-      <c r="J1" s="1" t="inlineStr"/>
-      <c r="K1" s="1" t="inlineStr"/>
-      <c r="L1" s="1" t="inlineStr"/>
-      <c r="M1" s="1" t="inlineStr"/>
-      <c r="N1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="N2" s="3" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>HACKATHON PARTICIPANTS</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="4" customHeight="1">
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="4" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="2" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -610,253 +652,167 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="N4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="8" customHeight="1">
+      <c r="A7" s="1" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr"/>
+      <c r="G7" s="1" t="inlineStr"/>
+      <c r="H7" s="1" t="inlineStr"/>
+      <c r="I7" s="1" t="inlineStr"/>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
+      <c r="L7" s="1" t="inlineStr"/>
+      <c r="M7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>HACKATHON PARTICIPANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  PECH Hackathon Event Tracking  |  CONFIDENTIAL</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="1" t="n"/>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="n"/>
-      <c r="K6" s="1" t="n"/>
-      <c r="L6" s="1" t="n"/>
-      <c r="M6" s="1" t="n"/>
-      <c r="N6" s="1" t="n"/>
-    </row>
-    <row r="7" ht="8" customHeight="1"/>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
+      <c r="L12" s="1" t="n"/>
+      <c r="M12" s="1" t="n"/>
+      <c r="N12" s="1" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  HACKATHON PARTICIPANTS REGISTER</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="8" t="n"/>
-      <c r="M8" s="8" t="n"/>
-      <c r="N8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Participant/Team</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Team Size</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Track</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Contact Email</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Registration Date</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Project Name</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Demo Link</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>R1 Score</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>R2 Score</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>Final Score</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Prize</t>
         </is>
       </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="10" t="n"/>
-      <c r="M10" s="10" t="n"/>
-      <c r="N10" s="10" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
-      <c r="N11" s="11" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="10" t="n"/>
-      <c r="M12" s="10" t="n"/>
-      <c r="N12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
-      <c r="M13" s="11" t="n"/>
-      <c r="N13" s="11" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="10" t="n"/>
-      <c r="M14" s="10" t="n"/>
-      <c r="N14" s="10" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n"/>
-      <c r="I15" s="11" t="n"/>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="11" t="n"/>
-      <c r="L15" s="11" t="n"/>
-      <c r="M15" s="11" t="n"/>
-      <c r="N15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
@@ -874,7 +830,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="11" t="n"/>
@@ -892,7 +848,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
@@ -910,7 +866,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B19" s="11" t="n"/>
       <c r="C19" s="11" t="n"/>
@@ -928,7 +884,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
@@ -946,7 +902,7 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="11" t="n"/>
@@ -964,7 +920,7 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
@@ -982,7 +938,7 @@
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="11" t="n"/>
@@ -1000,7 +956,7 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
@@ -1018,7 +974,7 @@
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
@@ -1036,7 +992,7 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
@@ -1054,7 +1010,7 @@
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
@@ -1072,7 +1028,7 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
@@ -1090,7 +1046,7 @@
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
@@ -1108,7 +1064,7 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
@@ -1126,7 +1082,7 @@
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="11" t="n"/>
@@ -1144,7 +1100,7 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
@@ -1162,7 +1118,7 @@
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="11" t="n"/>
@@ -1180,7 +1136,7 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
@@ -1198,7 +1154,7 @@
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
@@ -1216,7 +1172,7 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
@@ -1234,7 +1190,7 @@
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="11" t="n"/>
@@ -1252,7 +1208,7 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
@@ -1270,7 +1226,7 @@
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
@@ -1288,7 +1244,7 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
@@ -1306,7 +1262,7 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="11" t="n"/>
@@ -1324,7 +1280,7 @@
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="10" t="n"/>
@@ -1342,7 +1298,7 @@
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B43" s="11" t="n"/>
       <c r="C43" s="11" t="n"/>
@@ -1360,7 +1316,7 @@
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
@@ -1378,7 +1334,7 @@
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B45" s="11" t="n"/>
       <c r="C45" s="11" t="n"/>
@@ -1396,7 +1352,7 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
@@ -1414,7 +1370,7 @@
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B47" s="11" t="n"/>
       <c r="C47" s="11" t="n"/>
@@ -1432,7 +1388,7 @@
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
@@ -1450,7 +1406,7 @@
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B49" s="11" t="n"/>
       <c r="C49" s="11" t="n"/>
@@ -1468,7 +1424,7 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
@@ -1486,7 +1442,7 @@
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B51" s="11" t="n"/>
       <c r="C51" s="11" t="n"/>
@@ -1504,7 +1460,7 @@
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
@@ -1522,7 +1478,7 @@
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B53" s="11" t="n"/>
       <c r="C53" s="11" t="n"/>
@@ -1540,7 +1496,7 @@
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
@@ -1558,7 +1514,7 @@
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B55" s="11" t="n"/>
       <c r="C55" s="11" t="n"/>
@@ -1576,7 +1532,7 @@
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
@@ -1594,7 +1550,7 @@
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B57" s="11" t="n"/>
       <c r="C57" s="11" t="n"/>
@@ -1612,7 +1568,7 @@
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
@@ -1630,7 +1586,7 @@
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B59" s="11" t="n"/>
       <c r="C59" s="11" t="n"/>
@@ -1646,65 +1602,204 @@
       <c r="M59" s="11" t="n"/>
       <c r="N59" s="11" t="n"/>
     </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="10" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="10" t="n"/>
+    </row>
     <row r="61" ht="3" customHeight="1">
-      <c r="A61" s="5" t="n"/>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="5" t="n"/>
-      <c r="D61" s="5" t="n"/>
-      <c r="E61" s="5" t="n"/>
-      <c r="F61" s="5" t="n"/>
-      <c r="G61" s="5" t="n"/>
-      <c r="H61" s="5" t="n"/>
-      <c r="I61" s="5" t="n"/>
-      <c r="J61" s="5" t="n"/>
-      <c r="K61" s="5" t="n"/>
-      <c r="L61" s="5" t="n"/>
-      <c r="M61" s="5" t="n"/>
-      <c r="N61" s="5" t="n"/>
+      <c r="A61" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="11" t="n"/>
+      <c r="G61" s="11" t="n"/>
+      <c r="H61" s="11" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="11" t="n"/>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="11" t="n"/>
+      <c r="M61" s="11" t="n"/>
+      <c r="N61" s="11" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" s="10" t="n">
+        <v>47</v>
+      </c>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="10" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="10" t="n"/>
+    </row>
+    <row r="63" ht="3" customHeight="1">
+      <c r="A63" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="B63" s="11" t="n"/>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="11" t="n"/>
+      <c r="F63" s="11" t="n"/>
+      <c r="G63" s="11" t="n"/>
+      <c r="H63" s="11" t="n"/>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="11" t="n"/>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="11" t="n"/>
+      <c r="M63" s="11" t="n"/>
+      <c r="N63" s="11" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>49</v>
+      </c>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="11" t="n"/>
+      <c r="F65" s="11" t="n"/>
+      <c r="G65" s="11" t="n"/>
+      <c r="H65" s="11" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="11" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="11" t="n"/>
+      <c r="M65" s="11" t="n"/>
+      <c r="N65" s="11" t="n"/>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="5" t="n"/>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="n"/>
+      <c r="F67" s="5" t="n"/>
+      <c r="G67" s="5" t="n"/>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="5" t="n"/>
+      <c r="J67" s="5" t="n"/>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
         </is>
       </c>
-      <c r="B62" s="13" t="n"/>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="13" t="n"/>
-      <c r="H62" s="13" t="n"/>
-      <c r="I62" s="13" t="n"/>
-      <c r="J62" s="13" t="n"/>
-      <c r="K62" s="13" t="n"/>
-      <c r="L62" s="13" t="n"/>
-      <c r="M62" s="13" t="n"/>
-      <c r="N62" s="13" t="n"/>
-    </row>
-    <row r="63" ht="3" customHeight="1">
-      <c r="A63" s="1" t="n"/>
-      <c r="B63" s="1" t="n"/>
-      <c r="C63" s="1" t="n"/>
-      <c r="D63" s="1" t="n"/>
-      <c r="E63" s="1" t="n"/>
-      <c r="F63" s="1" t="n"/>
-      <c r="G63" s="1" t="n"/>
-      <c r="H63" s="1" t="n"/>
-      <c r="I63" s="1" t="n"/>
-      <c r="J63" s="1" t="n"/>
-      <c r="K63" s="1" t="n"/>
-      <c r="L63" s="1" t="n"/>
-      <c r="M63" s="1" t="n"/>
-      <c r="N63" s="1" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n"/>
+      <c r="B69" s="1" t="n"/>
+      <c r="C69" s="1" t="n"/>
+      <c r="D69" s="1" t="n"/>
+      <c r="E69" s="1" t="n"/>
+      <c r="F69" s="1" t="n"/>
+      <c r="G69" s="1" t="n"/>
+      <c r="H69" s="1" t="n"/>
+      <c r="I69" s="1" t="n"/>
+      <c r="J69" s="1" t="n"/>
+      <c r="K69" s="1" t="n"/>
+      <c r="L69" s="1" t="n"/>
+      <c r="M69" s="1" t="n"/>
+      <c r="N69" s="1" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>PECH GROUP HOLDINGS LTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n"/>
+      <c r="B75" s="1" t="n"/>
+      <c r="C75" s="1" t="n"/>
+      <c r="D75" s="1" t="n"/>
+      <c r="E75" s="1" t="n"/>
+      <c r="F75" s="1" t="n"/>
+      <c r="G75" s="1" t="n"/>
+      <c r="H75" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A8:N8"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A62:N62"/>
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A74:H74"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1716,5 +1811,14 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
+    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/employment_xlsx/PECH_HACKATHON_RULES_AND_GUIDELINES.xlsx
+++ b/employment_xlsx/PECH_HACKATHON_RULES_AND_GUIDELINES.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hackathon Participants" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hackathon Participants'!$A$9:$N$59</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,34 +61,6 @@
       <i val="1"/>
       <color rgb="00999999"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="000099CC"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="00F5A623"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00888888"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00E8F4F8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="7"/>
     </font>
   </fonts>
   <fills count="8">
@@ -159,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,21 +164,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -279,36 +238,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1905000" cy="628650"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -600,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -619,31 +548,63 @@
     <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="6" customHeight="1">
+      <c r="A1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr"/>
+      <c r="G1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr"/>
+      <c r="I1" s="1" t="inlineStr"/>
+      <c r="J1" s="1" t="inlineStr"/>
+      <c r="K1" s="1" t="inlineStr"/>
+      <c r="L1" s="1" t="inlineStr"/>
+      <c r="M1" s="1" t="inlineStr"/>
+      <c r="N1" s="1" t="inlineStr"/>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PECH GROUP HOLDINGS LTD</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="4" customHeight="1">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="n"/>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="2" customHeight="1">
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>HACKATHON PARTICIPANTS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="4" customHeight="1">
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
@@ -652,167 +613,253 @@
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  Confidential</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="1" t="inlineStr"/>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr"/>
-      <c r="E7" s="1" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr"/>
-      <c r="G7" s="1" t="inlineStr"/>
-      <c r="H7" s="1" t="inlineStr"/>
-      <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr"/>
-      <c r="L7" s="1" t="inlineStr"/>
-      <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
-    </row>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="5" t="n"/>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  PECH Hackathon Event Tracking  |  CONFIDENTIAL</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="3" t="n"/>
+    </row>
+    <row r="6" ht="4" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="1" t="n"/>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="n"/>
+      <c r="K6" s="1" t="n"/>
+      <c r="L6" s="1" t="n"/>
+      <c r="M6" s="1" t="n"/>
+      <c r="N6" s="1" t="n"/>
+    </row>
+    <row r="7" ht="8" customHeight="1"/>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HACKATHON PARTICIPANTS REGISTER</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
+      <c r="J8" s="8" t="n"/>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
+      <c r="N8" s="8" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>HACKATHON PARTICIPANTS</t>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Participant/Team</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Team Size</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Track</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Registration Date</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>Demo Link</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>R1 Score</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>R2 Score</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Final Score</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>Prize</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
+      <c r="A10" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Lagos, Nigeria  |  pechgroupholdings.tech  |  PECH Hackathon Event Tracking  |  CONFIDENTIAL</t>
-        </is>
-      </c>
+      <c r="A11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="11" t="n"/>
+      <c r="H11" s="11" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="11" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="1" t="n"/>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
-      <c r="K12" s="1" t="n"/>
-      <c r="L12" s="1" t="n"/>
-      <c r="M12" s="1" t="n"/>
-      <c r="N12" s="1" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="A12" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="11" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HACKATHON PARTICIPANTS REGISTER</t>
-        </is>
-      </c>
+      <c r="A14" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Participant/Team</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>Team Size</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Track</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>Contact Email</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Registration Date</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>Project Name</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Demo Link</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>R1 Score</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>R2 Score</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>Final Score</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>Prize</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="A15" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="10" t="n"/>
@@ -830,7 +877,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B17" s="11" t="n"/>
       <c r="C17" s="11" t="n"/>
@@ -848,7 +895,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="10" t="n"/>
@@ -866,7 +913,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B19" s="11" t="n"/>
       <c r="C19" s="11" t="n"/>
@@ -884,7 +931,7 @@
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="n"/>
       <c r="C20" s="10" t="n"/>
@@ -902,7 +949,7 @@
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="11" t="n"/>
@@ -920,7 +967,7 @@
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="n"/>
       <c r="C22" s="10" t="n"/>
@@ -938,7 +985,7 @@
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="n"/>
       <c r="C23" s="11" t="n"/>
@@ -956,7 +1003,7 @@
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
@@ -974,7 +1021,7 @@
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B25" s="11" t="n"/>
       <c r="C25" s="11" t="n"/>
@@ -992,7 +1039,7 @@
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="n"/>
       <c r="C26" s="10" t="n"/>
@@ -1010,7 +1057,7 @@
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B27" s="11" t="n"/>
       <c r="C27" s="11" t="n"/>
@@ -1028,7 +1075,7 @@
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
@@ -1046,7 +1093,7 @@
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
@@ -1064,7 +1111,7 @@
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B30" s="10" t="n"/>
       <c r="C30" s="10" t="n"/>
@@ -1082,7 +1129,7 @@
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B31" s="11" t="n"/>
       <c r="C31" s="11" t="n"/>
@@ -1100,7 +1147,7 @@
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B32" s="10" t="n"/>
       <c r="C32" s="10" t="n"/>
@@ -1118,7 +1165,7 @@
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B33" s="11" t="n"/>
       <c r="C33" s="11" t="n"/>
@@ -1136,7 +1183,7 @@
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
@@ -1154,7 +1201,7 @@
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B35" s="11" t="n"/>
       <c r="C35" s="11" t="n"/>
@@ -1172,7 +1219,7 @@
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
@@ -1190,7 +1237,7 @@
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B37" s="11" t="n"/>
       <c r="C37" s="11" t="n"/>
@@ -1208,7 +1255,7 @@
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
@@ -1226,7 +1273,7 @@
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B39" s="11" t="n"/>
       <c r="C39" s="11" t="n"/>
@@ -1244,7 +1291,7 @@
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B40" s="10" t="n"/>
       <c r="C40" s="10" t="n"/>
@@ -1262,7 +1309,7 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B41" s="11" t="n"/>
       <c r="C41" s="11" t="n"/>
@@ -1280,7 +1327,7 @@
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B42" s="10" t="n"/>
       <c r="C42" s="10" t="n"/>
@@ -1298,7 +1345,7 @@
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B43" s="11" t="n"/>
       <c r="C43" s="11" t="n"/>
@@ -1316,7 +1363,7 @@
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
@@ -1334,7 +1381,7 @@
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B45" s="11" t="n"/>
       <c r="C45" s="11" t="n"/>
@@ -1352,7 +1399,7 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B46" s="10" t="n"/>
       <c r="C46" s="10" t="n"/>
@@ -1370,7 +1417,7 @@
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B47" s="11" t="n"/>
       <c r="C47" s="11" t="n"/>
@@ -1388,7 +1435,7 @@
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B48" s="10" t="n"/>
       <c r="C48" s="10" t="n"/>
@@ -1406,7 +1453,7 @@
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B49" s="11" t="n"/>
       <c r="C49" s="11" t="n"/>
@@ -1424,7 +1471,7 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B50" s="10" t="n"/>
       <c r="C50" s="10" t="n"/>
@@ -1442,7 +1489,7 @@
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B51" s="11" t="n"/>
       <c r="C51" s="11" t="n"/>
@@ -1460,7 +1507,7 @@
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B52" s="10" t="n"/>
       <c r="C52" s="10" t="n"/>
@@ -1478,7 +1525,7 @@
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B53" s="11" t="n"/>
       <c r="C53" s="11" t="n"/>
@@ -1496,7 +1543,7 @@
     </row>
     <row r="54">
       <c r="A54" s="10" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B54" s="10" t="n"/>
       <c r="C54" s="10" t="n"/>
@@ -1514,7 +1561,7 @@
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B55" s="11" t="n"/>
       <c r="C55" s="11" t="n"/>
@@ -1532,7 +1579,7 @@
     </row>
     <row r="56">
       <c r="A56" s="10" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B56" s="10" t="n"/>
       <c r="C56" s="10" t="n"/>
@@ -1550,7 +1597,7 @@
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B57" s="11" t="n"/>
       <c r="C57" s="11" t="n"/>
@@ -1568,7 +1615,7 @@
     </row>
     <row r="58">
       <c r="A58" s="10" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B58" s="10" t="n"/>
       <c r="C58" s="10" t="n"/>
@@ -1586,7 +1633,7 @@
     </row>
     <row r="59">
       <c r="A59" s="11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B59" s="11" t="n"/>
       <c r="C59" s="11" t="n"/>
@@ -1602,204 +1649,66 @@
       <c r="M59" s="11" t="n"/>
       <c r="N59" s="11" t="n"/>
     </row>
-    <row r="60">
-      <c r="A60" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="B60" s="10" t="n"/>
-      <c r="C60" s="10" t="n"/>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="10" t="n"/>
-      <c r="G60" s="10" t="n"/>
-      <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="n"/>
-      <c r="J60" s="10" t="n"/>
-      <c r="K60" s="10" t="n"/>
-      <c r="L60" s="10" t="n"/>
-      <c r="M60" s="10" t="n"/>
-      <c r="N60" s="10" t="n"/>
-    </row>
     <row r="61" ht="3" customHeight="1">
-      <c r="A61" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="B61" s="11" t="n"/>
-      <c r="C61" s="11" t="n"/>
-      <c r="D61" s="11" t="n"/>
-      <c r="E61" s="11" t="n"/>
-      <c r="F61" s="11" t="n"/>
-      <c r="G61" s="11" t="n"/>
-      <c r="H61" s="11" t="n"/>
-      <c r="I61" s="11" t="n"/>
-      <c r="J61" s="11" t="n"/>
-      <c r="K61" s="11" t="n"/>
-      <c r="L61" s="11" t="n"/>
-      <c r="M61" s="11" t="n"/>
-      <c r="N61" s="11" t="n"/>
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="10" t="n">
-        <v>47</v>
-      </c>
-      <c r="B62" s="10" t="n"/>
-      <c r="C62" s="10" t="n"/>
-      <c r="D62" s="10" t="n"/>
-      <c r="E62" s="10" t="n"/>
-      <c r="F62" s="10" t="n"/>
-      <c r="G62" s="10" t="n"/>
-      <c r="H62" s="10" t="n"/>
-      <c r="I62" s="10" t="n"/>
-      <c r="J62" s="10" t="n"/>
-      <c r="K62" s="10" t="n"/>
-      <c r="L62" s="10" t="n"/>
-      <c r="M62" s="10" t="n"/>
-      <c r="N62" s="10" t="n"/>
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="n"/>
+      <c r="C62" s="13" t="n"/>
+      <c r="D62" s="13" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="13" t="n"/>
+      <c r="G62" s="13" t="n"/>
+      <c r="H62" s="13" t="n"/>
+      <c r="I62" s="13" t="n"/>
+      <c r="J62" s="13" t="n"/>
+      <c r="K62" s="13" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="13" t="n"/>
+      <c r="N62" s="13" t="n"/>
     </row>
     <row r="63" ht="3" customHeight="1">
-      <c r="A63" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="B63" s="11" t="n"/>
-      <c r="C63" s="11" t="n"/>
-      <c r="D63" s="11" t="n"/>
-      <c r="E63" s="11" t="n"/>
-      <c r="F63" s="11" t="n"/>
-      <c r="G63" s="11" t="n"/>
-      <c r="H63" s="11" t="n"/>
-      <c r="I63" s="11" t="n"/>
-      <c r="J63" s="11" t="n"/>
-      <c r="K63" s="11" t="n"/>
-      <c r="L63" s="11" t="n"/>
-      <c r="M63" s="11" t="n"/>
-      <c r="N63" s="11" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="B64" s="10" t="n"/>
-      <c r="C64" s="10" t="n"/>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
-      <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
-      <c r="N64" s="10" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="B65" s="11" t="n"/>
-      <c r="C65" s="11" t="n"/>
-      <c r="D65" s="11" t="n"/>
-      <c r="E65" s="11" t="n"/>
-      <c r="F65" s="11" t="n"/>
-      <c r="G65" s="11" t="n"/>
-      <c r="H65" s="11" t="n"/>
-      <c r="I65" s="11" t="n"/>
-      <c r="J65" s="11" t="n"/>
-      <c r="K65" s="11" t="n"/>
-      <c r="L65" s="11" t="n"/>
-      <c r="M65" s="11" t="n"/>
-      <c r="N65" s="11" t="n"/>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="5" t="n"/>
-      <c r="B67" s="5" t="n"/>
-      <c r="C67" s="5" t="n"/>
-      <c r="D67" s="5" t="n"/>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="n"/>
-      <c r="I67" s="5" t="n"/>
-      <c r="J67" s="5" t="n"/>
-      <c r="K67" s="5" t="n"/>
-      <c r="L67" s="5" t="n"/>
-      <c r="M67" s="5" t="n"/>
-      <c r="N67" s="5" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>PECH Group Holdings Ltd  |  Confidential  |  pechgroupholdings.tech  |  Technology &amp; Infrastructure Enablers for People</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n"/>
-      <c r="B69" s="1" t="n"/>
-      <c r="C69" s="1" t="n"/>
-      <c r="D69" s="1" t="n"/>
-      <c r="E69" s="1" t="n"/>
-      <c r="F69" s="1" t="n"/>
-      <c r="G69" s="1" t="n"/>
-      <c r="H69" s="1" t="n"/>
-      <c r="I69" s="1" t="n"/>
-      <c r="J69" s="1" t="n"/>
-      <c r="K69" s="1" t="n"/>
-      <c r="L69" s="1" t="n"/>
-      <c r="M69" s="1" t="n"/>
-      <c r="N69" s="1" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="17" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="17" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t>PECH GROUP HOLDINGS LTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="18" t="inlineStr">
-        <is>
-          <t>Confidential — PECH Group Holdings Ltd — Lagos, Nigeria — pechgroupholdings.tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="n"/>
-      <c r="B75" s="1" t="n"/>
-      <c r="C75" s="1" t="n"/>
-      <c r="D75" s="1" t="n"/>
-      <c r="E75" s="1" t="n"/>
-      <c r="F75" s="1" t="n"/>
-      <c r="G75" s="1" t="n"/>
-      <c r="H75" s="1" t="n"/>
+      <c r="A63" s="1" t="n"/>
+      <c r="B63" s="1" t="n"/>
+      <c r="C63" s="1" t="n"/>
+      <c r="D63" s="1" t="n"/>
+      <c r="E63" s="1" t="n"/>
+      <c r="F63" s="1" t="n"/>
+      <c r="G63" s="1" t="n"/>
+      <c r="H63" s="1" t="n"/>
+      <c r="I63" s="1" t="n"/>
+      <c r="J63" s="1" t="n"/>
+      <c r="K63" s="1" t="n"/>
+      <c r="L63" s="1" t="n"/>
+      <c r="M63" s="1" t="n"/>
+      <c r="N63" s="1" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <autoFilter ref="A9:N59"/>
+  <mergeCells count="5">
     <mergeCell ref="A8:N8"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A62:N62"/>
-    <mergeCell ref="A73:H73"/>
-    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A74:H74"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="D10 D11 D12 D13 D14 D15 D16 D17 D18 D19 D20 D21 D22 D23 D24 D25 D26 D27 D28 D29 D30 D31 D32 D33 D34 D35 D36 D37 D38 D39 D40 D41 D42 D43 D44 D45 D46 D47 D48 D49 D50 D51 D52 D53 D54 D55 D56 D57 D58 D59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1810,15 +1719,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;8 PECH Group Holdings Ltd | Confidential</oddHeader>
-    <oddFooter>&amp;C&amp;7 PECH Group Holdings Ltd | Lagos, Nigeria | pechgroupholdings.tech</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>